--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="68">
   <si>
     <t>code</t>
   </si>
@@ -56,6 +56,9 @@
     <t>image_url</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>ARG-001</t>
   </si>
   <si>
@@ -104,7 +107,7 @@
     <t>Бүгд зөв</t>
   </si>
   <si>
-    <t>4</t>
+    <t>d</t>
   </si>
   <si>
     <t>ARG-003</t>
@@ -128,12 +131,27 @@
     <t>А ба В зөв</t>
   </si>
   <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
+    <t>ARG-004</t>
+  </si>
+  <si>
+    <t>Энэ асуулт номноос хасагдсан тул идэвхгүй байна.</t>
+  </si>
+  <si>
+    <t>Зөв хувилбар</t>
+  </si>
+  <si>
+    <t>Буруу хувилбар</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Багана</t>
   </si>
   <si>
@@ -146,10 +164,10 @@
     <t>Тийм</t>
   </si>
   <si>
-    <t>Асуултын дахин давтагдашгүй код (ж: NEZ-P247-18 = бүлэг, хуудас, асуултын дугаар).</t>
-  </si>
-  <si>
-    <t>Номын бүлгийн нэр. Ижил нэртэй бүлгүүд нэг Subject болж нэгдэнэ.</t>
+    <t>Асуултын дахин давтагдашгүй код (ж: NEZ-P247-18 = бүлэг, хуудас, асуултын дугаар). Импорт асуултыг ЭНЭ кодоор нь таньдаг тул кодыг дараа нь өөрчлөхгүй.</t>
+  </si>
+  <si>
+    <t>Номын бүлгийн нэр. Ижил нэртэй бүлгүүд нэг Subject болж нэгдэнэ. Импорт судлагдахууныг НЭРЭЭР нь тааруулдаг.</t>
   </si>
   <si>
     <t>Асуултын бүтэн текст (кирилл). Хувилбарын үсгийг оруулахгүй.</t>
@@ -182,6 +200,9 @@
     <t>Асуултад зураг байвал түүний URL.</t>
   </si>
   <si>
+    <t>"1" = идэвхтэй, "0" = идэвхгүй (санд үлдэнэ, гэхдээ дадлага/шалгалтад гарахгүй). Нүдийг хоосон орхивол одоогийн төлөв нь хэвээр үлдэнэ. Энэ багана огт байхгүй файл (хуучин файлууд) хэвийн импортлогдож, ямар ч асуултын идэвхийг өөрчлөхгүй.</t>
+  </si>
+  <si>
     <t>Анхаарах</t>
   </si>
   <si>
@@ -189,6 +210,9 @@
   </si>
   <si>
     <t>Зөв хариултыг таамаглаж бөглөж болохгүй — номын хариултын түлхүүрээс авна.</t>
+  </si>
+  <si>
+    <t>Байгаа асуултын зөв хариултыг өөрчилбөл тухайн асуултыг хариулсан хэрэглэгчдийн давтлага тэглэгдэнэ; админ хэсэг үүнийг тусад нь баталгаажуулж асууна.</t>
   </si>
   <si>
     <t>Шалгах: pnpm import:questions &lt;файл&gt; --dry-run</t>
@@ -578,17 +602,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="9" width="42" customWidth="1"/>
     <col min="10" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="14" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,137 +655,196 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4" t="s">
         <v>39</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -782,13 +865,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -796,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -807,10 +890,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -818,21 +901,21 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -840,10 +923,10 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -851,10 +934,10 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -862,10 +945,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -873,10 +956,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -884,54 +967,76 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
